--- a/src/main/resources/MRF_ANNOUNCEMENT_LOADING_CIQ_PREPROD.xlsx
+++ b/src/main/resources/MRF_ANNOUNCEMENT_LOADING_CIQ_PREPROD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nswamy\AppData\Roaming\MobaXterm\slash\FTPRemoteFiles\104\1\A1TUJ88U@172.16.10.138\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Nokia\workspace\ciq-processor\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4E7204E-6FD5-440A-AA5C-DD6F18D045FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7BCFAC81-92F2-44E6-8751-B42A643D75A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{384DB82A-632B-44D1-941C-FAF965B93303}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{384DB82A-632B-44D1-941C-FAF965B93303}"/>
   </bookViews>
   <sheets>
     <sheet name="INDEX" sheetId="4" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="42">
   <si>
     <t>CRGROUP</t>
   </si>
@@ -154,7 +154,16 @@
     <t>NODE</t>
   </si>
   <si>
-    <t>root@postfix-vm.localdomain</t>
+    <t>root4@postfix-vm.localdomain</t>
+  </si>
+  <si>
+    <t>root5@postfix-vm.localdomain</t>
+  </si>
+  <si>
+    <t>root13@postfix-vm.localdomain,root14@postfix-vm.localdomain</t>
+  </si>
+  <si>
+    <t>root11@postfix-vm.localdomain</t>
   </si>
 </sst>
 </file>
@@ -613,7 +622,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="9.453125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="24.81640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="51.7265625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.36328125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="10.90625" customWidth="1"/>
   </cols>
@@ -637,7 +646,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>5</v>
@@ -651,7 +660,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>7</v>
@@ -662,11 +671,9 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>38</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="B4" s="7"/>
       <c r="C4" s="4" t="s">
         <v>9</v>
       </c>
@@ -693,7 +700,7 @@
         <v>12</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>13</v>
@@ -711,11 +718,10 @@
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="B2" r:id="rId1" xr:uid="{E932DC44-7CA2-4802-8078-D1AB9EE1D448}"/>
-    <hyperlink ref="B3" r:id="rId2" xr:uid="{9C3303AD-6B25-4B3C-BCE7-92E9280EEB6D}"/>
-    <hyperlink ref="B4" r:id="rId3" xr:uid="{21C8E63E-13AE-45D6-835A-8DE7A4D021C8}"/>
-    <hyperlink ref="B5" r:id="rId4" xr:uid="{6B5CEC58-304C-436B-BE50-4A661890604E}"/>
-    <hyperlink ref="B6" r:id="rId5" xr:uid="{CE4D913A-F4B7-4204-A764-8A423D1CB111}"/>
+    <hyperlink ref="B5" r:id="rId1" xr:uid="{6B5CEC58-304C-436B-BE50-4A661890604E}"/>
+    <hyperlink ref="B6" r:id="rId2" xr:uid="{CE4D913A-F4B7-4204-A764-8A423D1CB111}"/>
+    <hyperlink ref="B3" r:id="rId3" xr:uid="{9C3303AD-6B25-4B3C-BCE7-92E9280EEB6D}"/>
+    <hyperlink ref="B2" r:id="rId4" display="root11@postfix-vm.localdomain,root12@postfix-vm.localdomain" xr:uid="{E932DC44-7CA2-4802-8078-D1AB9EE1D448}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
